--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272034</v>
+        <v>121272033</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319468</v>
+        <v>319487</v>
       </c>
       <c r="R2" t="n">
-        <v>6521396</v>
+        <v>6521423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272033</v>
+        <v>121272034</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319487</v>
+        <v>319468</v>
       </c>
       <c r="R3" t="n">
-        <v>6521423</v>
+        <v>6521396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272033</v>
+        <v>121272035</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>97035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319487</v>
+        <v>319482</v>
       </c>
       <c r="R2" t="n">
-        <v>6521423</v>
+        <v>6521420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272034</v>
+        <v>121272033</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319468</v>
+        <v>319487</v>
       </c>
       <c r="R3" t="n">
-        <v>6521396</v>
+        <v>6521423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272035</v>
+        <v>121272034</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319482</v>
+        <v>319468</v>
       </c>
       <c r="R4" t="n">
-        <v>6521420</v>
+        <v>6521396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272035</v>
       </c>
       <c r="B2" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272035</v>
+        <v>121272033</v>
       </c>
       <c r="B2" t="n">
-        <v>97048</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319482</v>
+        <v>319487</v>
       </c>
       <c r="R2" t="n">
-        <v>6521420</v>
+        <v>6521423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272033</v>
+        <v>121272034</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319487</v>
+        <v>319468</v>
       </c>
       <c r="R3" t="n">
-        <v>6521423</v>
+        <v>6521396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272034</v>
+        <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>97049</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319468</v>
+        <v>319482</v>
       </c>
       <c r="R4" t="n">
-        <v>6521396</v>
+        <v>6521420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272033</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272034</v>
+        <v>121272035</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319468</v>
+        <v>319482</v>
       </c>
       <c r="R3" t="n">
-        <v>6521396</v>
+        <v>6521420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272035</v>
+        <v>121272034</v>
       </c>
       <c r="B4" t="n">
-        <v>97049</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319482</v>
+        <v>319468</v>
       </c>
       <c r="R4" t="n">
-        <v>6521420</v>
+        <v>6521396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272033</v>
+        <v>121272035</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319487</v>
+        <v>319482</v>
       </c>
       <c r="R2" t="n">
-        <v>6521423</v>
+        <v>6521420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272035</v>
+        <v>121272034</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319482</v>
+        <v>319468</v>
       </c>
       <c r="R3" t="n">
-        <v>6521420</v>
+        <v>6521396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272034</v>
+        <v>121272033</v>
       </c>
       <c r="B4" t="n">
         <v>57370</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319468</v>
+        <v>319487</v>
       </c>
       <c r="R4" t="n">
-        <v>6521396</v>
+        <v>6521423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272035</v>
+        <v>121272033</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319482</v>
+        <v>319487</v>
       </c>
       <c r="R2" t="n">
-        <v>6521420</v>
+        <v>6521423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>121272034</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272033</v>
+        <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>97058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319487</v>
+        <v>319482</v>
       </c>
       <c r="R4" t="n">
-        <v>6521423</v>
+        <v>6521420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272033</v>
+        <v>121272034</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319487</v>
+        <v>319468</v>
       </c>
       <c r="R2" t="n">
-        <v>6521423</v>
+        <v>6521396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272034</v>
+        <v>121272033</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319468</v>
+        <v>319487</v>
       </c>
       <c r="R3" t="n">
-        <v>6521396</v>
+        <v>6521423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272034</v>
+        <v>121272035</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319468</v>
+        <v>319482</v>
       </c>
       <c r="R2" t="n">
-        <v>6521396</v>
+        <v>6521420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272033</v>
+        <v>121272034</v>
       </c>
       <c r="B3" t="n">
         <v>57372</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319487</v>
+        <v>319468</v>
       </c>
       <c r="R3" t="n">
-        <v>6521423</v>
+        <v>6521396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272035</v>
+        <v>121272033</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319482</v>
+        <v>319487</v>
       </c>
       <c r="R4" t="n">
-        <v>6521420</v>
+        <v>6521423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272035</v>
+        <v>121272034</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319482</v>
+        <v>319468</v>
       </c>
       <c r="R2" t="n">
-        <v>6521420</v>
+        <v>6521396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272034</v>
+        <v>121272035</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319468</v>
+        <v>319482</v>
       </c>
       <c r="R3" t="n">
-        <v>6521396</v>
+        <v>6521420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272035</v>
+        <v>121272033</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319482</v>
+        <v>319487</v>
       </c>
       <c r="R3" t="n">
-        <v>6521420</v>
+        <v>6521423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121272033</v>
+        <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319487</v>
+        <v>319482</v>
       </c>
       <c r="R4" t="n">
-        <v>6521423</v>
+        <v>6521420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272034</v>
+        <v>121272033</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319468</v>
+        <v>319487</v>
       </c>
       <c r="R2" t="n">
-        <v>6521396</v>
+        <v>6521423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272033</v>
+        <v>121272034</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>319487</v>
+        <v>319468</v>
       </c>
       <c r="R3" t="n">
-        <v>6521423</v>
+        <v>6521396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +882,7 @@
         <v>121272035</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43908-2024 artfynd.xlsx
+++ b/artfynd/A 43908-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121272033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121272034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,8 +988,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121272035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>